--- a/Full Participants.xlsx
+++ b/Full Participants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIMUN\NIMUN'26\Regsitration System\NIMUN-Registration-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A6F01F-E5BD-4335-9837-C151C0B5185D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC689CF0-7DEB-4E22-9D01-AAF32829D732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C368E04E-0B9E-4D4D-BD2F-6CE8907794F4}"/>
   </bookViews>
